--- a/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{BD78D437-AEF8-48E9-94A4-63475236AA11}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C315B5E-E963-4322-8CF0-01450874D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
-    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
+    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
+    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="123">
   <si>
     <t>Result</t>
   </si>
@@ -265,185 +265,157 @@
     <t>Payment app+correct Phone+wrong Lookup3 Label</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
-    <t>Mon Mar 09 20:07:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:08:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:09:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:09:43 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:10:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:11:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Mon Mar 09 20:54:01 IST 2026</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:37:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:37:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:38:25 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:38:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:39:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:40:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:40:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:41:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:42:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:42:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:43:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:43:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:44:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:45:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:45:40 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:46:17 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:46:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:47:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:47:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:48:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:49:11 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:49:45 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:50:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:50:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:51:29 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 13:52:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:07:05 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:07:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:08:27 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:09:02 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:09:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:10:16 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:10:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:11:38 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:12:15 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:12:53 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:13:39 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:14:18 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:14:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:15:32 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:16:12 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:16:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:17:26 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:17:59 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:18:35 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:19:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:19:47 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 11 16:20:27 IST 2026</t>
+    <t>Wed Mar 25 17:04:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:05:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:06:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:06:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:07:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:08:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:09:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:09:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:10:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:11:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:11:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:12:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:12:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:13:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:13:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:14:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:15:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:15:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:16:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:16:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:17:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:17:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:18:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:18:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:41:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:42:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:42:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:43:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:43:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:44:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:44:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:45:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:46:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:46:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:47:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:48:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:48:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:49:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:49:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:50:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:50:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:51:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:51:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:52:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Mar 25 17:52:52 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -502,37 +474,37 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -549,10 +521,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -587,7 +559,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -639,7 +611,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -750,21 +722,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -781,7 +753,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -853,29 +825,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:L27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
-    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="18.7265625" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="3" width="9.0" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
-    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="11.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
+    <col min="5" max="5" width="18.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9" style="3" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -913,12 +885,12 @@
         <v>66</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s">
         <v>75</v>
-      </c>
-      <c r="B2" t="s">
-        <v>84</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -933,12 +905,12 @@
         <v>50020002</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -953,12 +925,12 @@
         <v>40</v>
       </c>
     </row>
-    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -973,12 +945,12 @@
         <v>42</v>
       </c>
     </row>
-    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -993,12 +965,12 @@
         <v>41</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>59</v>
@@ -1013,12 +985,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1033,12 +1005,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1053,12 +1025,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1088,12 +1060,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1111,12 +1083,12 @@
         <v>40</v>
       </c>
     </row>
-    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1134,12 +1106,12 @@
         <v>41</v>
       </c>
     </row>
-    <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>39</v>
@@ -1157,12 +1129,12 @@
         <v>42</v>
       </c>
     </row>
-    <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1180,12 +1152,12 @@
         <v>42</v>
       </c>
     </row>
-    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1203,12 +1175,12 @@
         <v>41</v>
       </c>
     </row>
-    <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1226,12 +1198,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1249,12 +1221,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="17" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>60</v>
@@ -1272,12 +1244,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="13" r="18" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1295,12 +1267,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="19" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1318,12 +1290,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="20" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>61</v>
@@ -1341,12 +1313,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row ht="25" r="21" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:11" ht="25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>58</v>
@@ -1367,12 +1339,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row customHeight="1" ht="18" r="22" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1390,12 +1362,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="23" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1413,12 +1385,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="24" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>62</v>
@@ -1436,12 +1408,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row customHeight="1" ht="17.5" r="25" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1459,12 +1431,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row ht="13" r="26" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1482,12 +1454,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row ht="13" r="27" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:11" ht="13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>63</v>
@@ -1507,32 +1479,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:M23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="5" width="10.90625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="6" width="30.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="3" width="7.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="3" width="18.453125" collapsed="true"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="8.81640625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="3" width="9.81640625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="3" width="15.54296875" collapsed="true"/>
-    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="3" width="13.81640625" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="3" width="13.0" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="5" width="45.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="3" width="8.7265625" collapsed="true"/>
+    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="10.90625" style="5" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="30.26953125" style="6" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="7.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="18.453125" style="3" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="8.81640625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="9.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="15.54296875" style="3" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
+    <col min="10" max="10" width="13.81640625" style="3" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="13" style="3" customWidth="1" collapsed="1"/>
+    <col min="12" max="12" width="45.1796875" style="5" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3" collapsed="1"/>
   </cols>
   <sheetData>
-    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1570,12 +1542,12 @@
         <v>8</v>
       </c>
     </row>
-    <row ht="13" r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1593,12 +1565,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="13" r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1616,12 +1588,12 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="14.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1639,12 +1611,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1662,12 +1634,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="13" r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>43</v>
@@ -1685,12 +1657,12 @@
         <v>7</v>
       </c>
     </row>
-    <row customHeight="1" ht="17.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>44</v>
@@ -1708,12 +1680,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>45</v>
@@ -1734,12 +1706,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>46</v>
@@ -1760,12 +1732,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>48</v>
@@ -1786,12 +1758,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>47</v>
@@ -1812,12 +1784,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>53</v>
@@ -1838,12 +1810,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>54</v>
@@ -1864,12 +1836,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>55</v>
@@ -1890,12 +1862,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>49</v>
@@ -1916,12 +1888,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>50</v>
@@ -1942,12 +1914,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="17" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>51</v>
@@ -1968,12 +1940,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="18" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>52</v>
@@ -1994,12 +1966,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="19" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>68</v>
@@ -2017,12 +1989,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="20" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>70</v>
@@ -2043,12 +2015,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="21" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>71</v>
@@ -2069,12 +2041,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="22" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>72</v>
@@ -2095,12 +2067,12 @@
         <v>7</v>
       </c>
     </row>
-    <row ht="25" r="23" spans="3:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="25" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>73</v>
@@ -2122,7 +2094,7 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C315B5E-E963-4322-8CF0-01450874D7AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC10805-9208-4634-987A-FA3B91D38AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
   </bookViews>
   <sheets>
     <sheet name="BFLU" sheetId="1" r:id="rId1"/>
     <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
+    <sheet name="BFLU_1Result" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="127">
   <si>
     <t>Result</t>
   </si>
@@ -268,148 +269,160 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Wed Mar 25 17:04:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:05:44 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:06:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:06:52 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:07:22 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:08:00 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:08:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:09:07 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:09:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:10:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:10:50 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:11:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:11:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:12:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:12:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:13:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:13:54 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:14:28 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:15:01 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:15:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:16:09 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:16:41 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:17:14 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:17:46 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:18:20 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:18:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:41:21 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:42:03 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:42:33 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:43:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:43:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:44:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:44:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:45:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:45:55 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:46:24 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:46:56 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:47:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:48:04 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:48:34 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:49:10 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:49:42 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:50:23 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:50:51 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:51:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:51:49 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:52:19 IST 2026</t>
-  </si>
-  <si>
-    <t>Wed Mar 25 17:52:52 IST 2026</t>
+    <t>Thu Jun 18 00:57:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:58:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 00:59:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:00:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:01:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:02:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:03:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:04:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:05:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:06:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:07:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:08:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:10:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:11:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:12:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:12:55 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:13:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:14:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:15:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:16:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:18:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:19:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:20:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:21:07 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:22:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:45:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:46:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:47:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:48:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:49:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:50:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:50:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:51:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:52:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:53:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:54:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:55:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:56:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:57:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:58:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:59:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 01:59:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:00:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:01:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:02:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:03:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 18 02:04:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Payment app+ 1st + 2nd +3rd lookup</t>
+  </si>
+  <si>
+    <t>Payment app+ Company Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment app+ CAN </t>
+  </si>
+  <si>
+    <t>Thu Jun 18 20:32:42 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -2097,4 +2110,108 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F588A9-FD8A-4996-A530-60A12E52C8E8}">
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.08984375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="33.90625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="8" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.1796875" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.26953125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="21.453125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="15.81640625" style="3" customWidth="1"/>
+    <col min="10" max="10" width="14.54296875" style="3" customWidth="1"/>
+    <col min="11" max="11" width="13.36328125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.7265625" style="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K2" s="7"/>
+    </row>
+    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="7"/>
+    </row>
+    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="F4" s="3">
+        <v>50020002</v>
+      </c>
+      <c r="K4" s="7"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t470258\Documents\VPS-Katalon\KatalonData\EmailTextToPay\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EC10805-9208-4634-987A-FA3B91D38AD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr documentId="13_ncr:1_{2EC10805-9208-4634-987A-FA3B91D38AD6}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}"/>
+    <workbookView activeTab="2" windowHeight="11500" windowWidth="19420" xWindow="-110" xr2:uid="{A171AD99-6CB3-481A-968B-971B4AF2105E}" yWindow="-110"/>
   </bookViews>
   <sheets>
-    <sheet name="BFLU" sheetId="1" r:id="rId1"/>
-    <sheet name="BFLUError" sheetId="2" r:id="rId2"/>
-    <sheet name="BFLU_1Result" sheetId="3" r:id="rId3"/>
+    <sheet name="BFLU" r:id="rId1" sheetId="1"/>
+    <sheet name="BFLUError" r:id="rId2" sheetId="2"/>
+    <sheet name="BFLU_1Result" r:id="rId3" sheetId="3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="177">
   <si>
     <t>Result</t>
   </si>
@@ -423,12 +423,163 @@
   </si>
   <si>
     <t>Thu Jun 18 20:32:42 IST 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:07:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:08:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:09:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:10:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:11:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:11:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:12:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:13:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:14:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:14:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:15:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:16:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:17:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:18:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:18:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:19:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:20:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:21:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:22:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:22:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:23:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:24:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:24:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:25:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:26:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:27:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:27:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:28:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:29:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:29:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:30:45 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:31:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:32:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:32:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:33:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:34:18 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:34:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:35:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:36:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:37:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:38:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:38:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:39:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:40:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:41:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:41:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:42:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:43:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Jun 29 13:43:57 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -487,37 +638,37 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
   <cellXfs count="8">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
+    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="3" numFmtId="49" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf applyAlignment="1" applyFont="1" borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf applyAlignment="1" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle builtinId="0" name="Normal" xfId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -534,10 +685,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -572,7 +723,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Display"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -624,7 +775,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin panose="02110004020202020204" typeface="Aptos Narrow"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -735,21 +886,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cap="flat" cmpd="sng" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -766,7 +917,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -838,29 +989,29 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" name="Office Theme" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:K27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="11.08984375" style="3" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="35.453125" style="6" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="8.7265625" style="3" collapsed="1"/>
-    <col min="5" max="5" width="18.7265625" style="3" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9" style="3" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="9.7265625" style="3" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="25.6328125" style="3" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="13.6328125" style="3" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="13.54296875" style="7" customWidth="1" collapsed="1"/>
-    <col min="12" max="16384" width="8.7265625" style="3" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="11.08984375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="6" width="35.453125" collapsed="true"/>
+    <col min="4" max="4" style="3" width="8.7265625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="3" width="18.7265625" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="3" width="9.0" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="3" width="9.7265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="3" width="25.6328125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="3" width="13.6328125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="7" width="13.54296875" collapsed="true"/>
+    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -898,12 +1049,12 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -918,12 +1069,12 @@
         <v>50020002</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>129</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -938,12 +1089,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -958,12 +1109,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>131</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -978,12 +1129,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>132</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>59</v>
@@ -998,12 +1149,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1018,12 +1169,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1038,12 +1189,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>135</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1073,12 +1224,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1096,12 +1247,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>137</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1119,12 +1270,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>39</v>
@@ -1142,12 +1293,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1165,12 +1316,12 @@
         <v>42</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1188,12 +1339,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>88</v>
+        <v>141</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1211,12 +1362,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>142</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1234,12 +1385,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>60</v>
@@ -1257,12 +1408,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1280,12 +1431,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1303,12 +1454,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>93</v>
+        <v>146</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>61</v>
@@ -1326,12 +1477,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>94</v>
+        <v>147</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>58</v>
@@ -1352,12 +1503,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="18" r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>95</v>
+        <v>148</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1375,12 +1526,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>96</v>
+        <v>149</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1398,12 +1549,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>74</v>
       </c>
       <c r="B24" t="s">
-        <v>97</v>
+        <v>150</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>62</v>
@@ -1421,12 +1572,12 @@
         <v>935960</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="17.5" r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>74</v>
       </c>
       <c r="B25" t="s">
-        <v>98</v>
+        <v>151</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1444,12 +1595,12 @@
         <v>428853</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>74</v>
       </c>
       <c r="B26" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1467,12 +1618,12 @@
         <v>311785</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>74</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>63</v>
@@ -1492,32 +1643,32 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:L23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.08984375" style="3" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="10.90625" style="5" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="30.26953125" style="6" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="7.81640625" style="3" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="18.453125" style="3" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="8.81640625" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="9.81640625" style="3" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="15.54296875" style="3" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="15.6328125" style="3" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="13.81640625" style="3" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="13" style="3" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="45.1796875" style="5" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="8.7265625" style="3" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="5" width="10.90625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="6" width="30.26953125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="3" width="7.81640625" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="3" width="18.453125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="8.81640625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="3" width="9.81640625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="3" width="15.54296875" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="3" width="15.6328125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="3" width="13.81640625" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="3" width="13.0" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="5" width="45.1796875" collapsed="true"/>
+    <col min="13" max="16384" style="3" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1555,12 +1706,12 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>74</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>155</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1578,12 +1729,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>156</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1601,12 +1752,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="14.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="14.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>103</v>
+        <v>157</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1624,12 +1775,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>74</v>
       </c>
       <c r="B5" t="s">
-        <v>104</v>
+        <v>158</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1647,12 +1798,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>105</v>
+        <v>159</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>43</v>
@@ -1670,12 +1821,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row customHeight="1" ht="17.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>160</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>44</v>
@@ -1693,12 +1844,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>107</v>
+        <v>161</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>45</v>
@@ -1719,12 +1870,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>46</v>
@@ -1745,12 +1896,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>109</v>
+        <v>163</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>48</v>
@@ -1771,12 +1922,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>164</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>47</v>
@@ -1797,12 +1948,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>74</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>165</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>53</v>
@@ -1823,12 +1974,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>74</v>
       </c>
       <c r="B13" t="s">
-        <v>112</v>
+        <v>166</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>54</v>
@@ -1849,12 +2000,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>113</v>
+        <v>167</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>55</v>
@@ -1875,12 +2026,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>74</v>
       </c>
       <c r="B15" t="s">
-        <v>114</v>
+        <v>168</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>49</v>
@@ -1901,12 +2052,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>169</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>50</v>
@@ -1927,12 +2078,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>74</v>
       </c>
       <c r="B17" t="s">
-        <v>116</v>
+        <v>170</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>51</v>
@@ -1953,12 +2104,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>74</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>171</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>52</v>
@@ -1979,12 +2130,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>74</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>172</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>68</v>
@@ -2002,12 +2153,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>74</v>
       </c>
       <c r="B20" t="s">
-        <v>119</v>
+        <v>173</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>70</v>
@@ -2028,12 +2179,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>74</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>71</v>
@@ -2054,12 +2205,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>74</v>
       </c>
       <c r="B22" t="s">
-        <v>121</v>
+        <v>175</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>72</v>
@@ -2080,12 +2231,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>74</v>
       </c>
       <c r="B23" t="s">
-        <v>122</v>
+        <v>176</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>73</v>
@@ -2107,31 +2258,31 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F588A9-FD8A-4996-A530-60A12E52C8E8}">
-  <dimension ref="A1:K4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F588A9-FD8A-4996-A530-60A12E52C8E8}">
+  <dimension ref="A1:L4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.08984375" style="3" customWidth="1"/>
-    <col min="3" max="3" width="33.90625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="8" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="25.1796875" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.453125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.26953125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="21.453125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="15.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="14.54296875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="13.36328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="3"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="6.0" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="3" width="17.08984375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="3" width="33.90625" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="3" width="8.0" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="3" width="25.1796875" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="3" width="14.453125" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="3" width="10.26953125" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="3" width="21.453125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="3" width="15.81640625" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="3" width="14.54296875" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="3" width="13.36328125" collapsed="true"/>
+    <col min="12" max="16384" style="3" width="8.7265625" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2166,7 +2317,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="25" x14ac:dyDescent="0.25">
+    <row ht="25" r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>74</v>
       </c>
@@ -2178,7 +2329,7 @@
       </c>
       <c r="K2" s="7"/>
     </row>
-    <row r="3" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>74</v>
       </c>
@@ -2190,12 +2341,12 @@
       </c>
       <c r="K3" s="7"/>
     </row>
-    <row r="4" spans="1:11" ht="13" x14ac:dyDescent="0.25">
+    <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>74</v>
       </c>
       <c r="B4" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>125</v>
@@ -2212,6 +2363,6 @@
       <c r="K4" s="7"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="301">
   <si>
     <t>Result</t>
   </si>
@@ -573,6 +573,378 @@
   </si>
   <si>
     <t>Mon Jun 29 13:43:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:33:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:35:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:36:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:37:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:38:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:39:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:40:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:41:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:43:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:44:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:46:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:46:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:47:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:48:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:49:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:50:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:51:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:52:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:53:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:54:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:55:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:56:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:57:17 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:58:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 13:58:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:01:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:03:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:04:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:05:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:05:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:06:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:07:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:08:33 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:09:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:10:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:11:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:11:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:12:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:13:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:14:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:15:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:16:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:17:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:18:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:18:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:19:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:20:34 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:21:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:22:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:22:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:23:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:24:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:25:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:26:16 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:27:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:27:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:28:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:29:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:30:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:31:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:32:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:32:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:33:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:34:20 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:35:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:35:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:36:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:37:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:38:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:39:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:39:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:40:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:41:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 03 14:42:14 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:27:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:29:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:29:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:30:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:31:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:32:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:33:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:34:04 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:34:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:35:49 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:36:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:38:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:39:02 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:39:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:40:38 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:41:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:42:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:43:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:44:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:44:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:45:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:46:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:47:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:48:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:49:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:49:59 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:50:54 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:51:41 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:52:25 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:53:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:53:47 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:54:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:55:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:56:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:56:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:57:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:58:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:59:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 17:59:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:00:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:01:24 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:02:10 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:02:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:03:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:04:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:05:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:05:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:06:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 18:07:23 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -997,7 +1369,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
@@ -1050,11 +1422,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>128</v>
+      <c r="A2" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s" s="3">
+        <v>252</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -1070,11 +1442,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>129</v>
+      <c r="A3" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s" s="3">
+        <v>253</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
@@ -1090,11 +1462,11 @@
       </c>
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>130</v>
+      <c r="A4" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>254</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>12</v>
@@ -1110,11 +1482,11 @@
       </c>
     </row>
     <row ht="13" r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>131</v>
+      <c r="A5" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s" s="3">
+        <v>255</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>13</v>
@@ -1130,11 +1502,11 @@
       </c>
     </row>
     <row ht="13" r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>132</v>
+      <c r="A6" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s" s="3">
+        <v>256</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>59</v>
@@ -1150,11 +1522,11 @@
       </c>
     </row>
     <row ht="13" r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>133</v>
+      <c r="A7" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s" s="3">
+        <v>257</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>28</v>
@@ -1170,11 +1542,11 @@
       </c>
     </row>
     <row ht="13" r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>134</v>
+      <c r="A8" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s" s="3">
+        <v>258</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>29</v>
@@ -1190,11 +1562,11 @@
       </c>
     </row>
     <row ht="13" r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>135</v>
+      <c r="A9" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s" s="3">
+        <v>259</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>9</v>
@@ -1225,11 +1597,11 @@
       </c>
     </row>
     <row ht="13" r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s">
-        <v>136</v>
+      <c r="A10" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s" s="3">
+        <v>260</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>15</v>
@@ -1248,11 +1620,11 @@
       </c>
     </row>
     <row ht="13" r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s">
-        <v>137</v>
+      <c r="A11" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s" s="3">
+        <v>261</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>14</v>
@@ -1271,11 +1643,11 @@
       </c>
     </row>
     <row ht="13" r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s">
-        <v>138</v>
+      <c r="A12" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s" s="3">
+        <v>262</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>39</v>
@@ -1294,11 +1666,11 @@
       </c>
     </row>
     <row customHeight="1" ht="18" r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>139</v>
+      <c r="A13" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s" s="3">
+        <v>263</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>16</v>
@@ -1317,11 +1689,11 @@
       </c>
     </row>
     <row ht="13" r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s">
-        <v>140</v>
+      <c r="A14" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s" s="3">
+        <v>264</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>17</v>
@@ -1340,11 +1712,11 @@
       </c>
     </row>
     <row customHeight="1" ht="14.5" r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>141</v>
+      <c r="A15" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s" s="3">
+        <v>265</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>30</v>
@@ -1363,11 +1735,11 @@
       </c>
     </row>
     <row ht="13" r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s">
-        <v>142</v>
+      <c r="A16" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s" s="3">
+        <v>266</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>31</v>
@@ -1386,11 +1758,11 @@
       </c>
     </row>
     <row ht="13" r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" t="s">
-        <v>143</v>
+      <c r="A17" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s" s="3">
+        <v>267</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>60</v>
@@ -1409,11 +1781,11 @@
       </c>
     </row>
     <row ht="13" r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" t="s">
-        <v>144</v>
+      <c r="A18" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s" s="3">
+        <v>268</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>32</v>
@@ -1432,11 +1804,11 @@
       </c>
     </row>
     <row ht="13" r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>145</v>
+      <c r="A19" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s" s="3">
+        <v>269</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>33</v>
@@ -1455,11 +1827,11 @@
       </c>
     </row>
     <row ht="13" r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s">
-        <v>146</v>
+      <c r="A20" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s" s="3">
+        <v>270</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>61</v>
@@ -1478,11 +1850,11 @@
       </c>
     </row>
     <row ht="25" r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" t="s">
-        <v>147</v>
+      <c r="A21" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="3">
+        <v>271</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>58</v>
@@ -1504,11 +1876,11 @@
       </c>
     </row>
     <row customHeight="1" ht="18" r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" t="s">
-        <v>148</v>
+      <c r="A22" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s" s="3">
+        <v>272</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>34</v>
@@ -1527,11 +1899,11 @@
       </c>
     </row>
     <row ht="13" r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s">
-        <v>149</v>
+      <c r="A23" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s" s="3">
+        <v>273</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>35</v>
@@ -1550,11 +1922,11 @@
       </c>
     </row>
     <row ht="13" r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>74</v>
-      </c>
-      <c r="B24" t="s">
-        <v>150</v>
+      <c r="A24" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B24" t="s" s="3">
+        <v>274</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>62</v>
@@ -1573,11 +1945,11 @@
       </c>
     </row>
     <row customHeight="1" ht="17.5" r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" t="s">
-        <v>151</v>
+      <c r="A25" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B25" t="s" s="3">
+        <v>275</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>36</v>
@@ -1596,11 +1968,11 @@
       </c>
     </row>
     <row ht="13" r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>74</v>
-      </c>
-      <c r="B26" t="s">
-        <v>152</v>
+      <c r="A26" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s" s="3">
+        <v>276</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>37</v>
@@ -1619,11 +1991,11 @@
       </c>
     </row>
     <row ht="13" r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>74</v>
-      </c>
-      <c r="B27" t="s">
-        <v>153</v>
+      <c r="A27" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B27" t="s" s="3">
+        <v>277</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>63</v>
@@ -1650,7 +2022,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="3" width="6.08984375" collapsed="true"/>
@@ -1707,11 +2079,11 @@
       </c>
     </row>
     <row ht="13" r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B2" t="s">
-        <v>155</v>
+      <c r="A2" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B2" t="s" s="5">
+        <v>279</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>20</v>
@@ -1730,11 +2102,11 @@
       </c>
     </row>
     <row ht="13" r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" t="s">
-        <v>156</v>
+      <c r="A3" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B3" t="s" s="5">
+        <v>280</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>21</v>
@@ -1753,11 +2125,11 @@
       </c>
     </row>
     <row customHeight="1" ht="14.5" r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>157</v>
+      <c r="A4" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s" s="5">
+        <v>281</v>
       </c>
       <c r="C4" s="6" t="s">
         <v>22</v>
@@ -1776,11 +2148,11 @@
       </c>
     </row>
     <row ht="25" r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>74</v>
-      </c>
-      <c r="B5" t="s">
-        <v>158</v>
+      <c r="A5" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B5" t="s" s="5">
+        <v>282</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>23</v>
@@ -1799,11 +2171,11 @@
       </c>
     </row>
     <row ht="13" r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>74</v>
-      </c>
-      <c r="B6" t="s">
-        <v>159</v>
+      <c r="A6" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B6" t="s" s="5">
+        <v>283</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>43</v>
@@ -1822,11 +2194,11 @@
       </c>
     </row>
     <row customHeight="1" ht="17.5" r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>74</v>
-      </c>
-      <c r="B7" t="s">
-        <v>160</v>
+      <c r="A7" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s" s="5">
+        <v>284</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>44</v>
@@ -1845,11 +2217,11 @@
       </c>
     </row>
     <row ht="25" r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>161</v>
+      <c r="A8" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B8" t="s" s="5">
+        <v>285</v>
       </c>
       <c r="C8" s="6" t="s">
         <v>45</v>
@@ -1871,11 +2243,11 @@
       </c>
     </row>
     <row ht="25" r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>162</v>
+      <c r="A9" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s" s="5">
+        <v>286</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>46</v>
@@ -1897,11 +2269,11 @@
       </c>
     </row>
     <row ht="25" r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>74</v>
-      </c>
-      <c r="B10" t="s">
-        <v>163</v>
+      <c r="A10" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B10" t="s" s="5">
+        <v>287</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>48</v>
@@ -1923,11 +2295,11 @@
       </c>
     </row>
     <row ht="25" r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" t="s">
-        <v>164</v>
+      <c r="A11" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B11" t="s" s="5">
+        <v>288</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>47</v>
@@ -1949,11 +2321,11 @@
       </c>
     </row>
     <row ht="25" r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>74</v>
-      </c>
-      <c r="B12" t="s">
-        <v>165</v>
+      <c r="A12" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B12" t="s" s="5">
+        <v>289</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>53</v>
@@ -1975,11 +2347,11 @@
       </c>
     </row>
     <row ht="25" r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>166</v>
+      <c r="A13" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B13" t="s" s="5">
+        <v>290</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>54</v>
@@ -2001,11 +2373,11 @@
       </c>
     </row>
     <row ht="25" r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>74</v>
-      </c>
-      <c r="B14" t="s">
-        <v>167</v>
+      <c r="A14" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B14" t="s" s="5">
+        <v>291</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>55</v>
@@ -2027,11 +2399,11 @@
       </c>
     </row>
     <row ht="25" r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>74</v>
-      </c>
-      <c r="B15" t="s">
-        <v>168</v>
+      <c r="A15" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B15" t="s" s="5">
+        <v>292</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>49</v>
@@ -2053,11 +2425,11 @@
       </c>
     </row>
     <row ht="25" r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>74</v>
-      </c>
-      <c r="B16" t="s">
-        <v>169</v>
+      <c r="A16" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B16" t="s" s="5">
+        <v>293</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>50</v>
@@ -2079,11 +2451,11 @@
       </c>
     </row>
     <row ht="25" r="17" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B17" t="s">
-        <v>170</v>
+      <c r="A17" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s" s="5">
+        <v>294</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>51</v>
@@ -2105,11 +2477,11 @@
       </c>
     </row>
     <row ht="25" r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" t="s">
-        <v>171</v>
+      <c r="A18" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s" s="5">
+        <v>295</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>52</v>
@@ -2131,11 +2503,11 @@
       </c>
     </row>
     <row ht="25" r="19" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>74</v>
-      </c>
-      <c r="B19" t="s">
-        <v>172</v>
+      <c r="A19" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B19" t="s" s="5">
+        <v>296</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>68</v>
@@ -2154,11 +2526,11 @@
       </c>
     </row>
     <row ht="25" r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>74</v>
-      </c>
-      <c r="B20" t="s">
-        <v>173</v>
+      <c r="A20" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B20" t="s" s="5">
+        <v>297</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>70</v>
@@ -2180,11 +2552,11 @@
       </c>
     </row>
     <row ht="25" r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B21" t="s">
-        <v>174</v>
+      <c r="A21" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B21" t="s" s="5">
+        <v>298</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>71</v>
@@ -2206,11 +2578,11 @@
       </c>
     </row>
     <row ht="25" r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>74</v>
-      </c>
-      <c r="B22" t="s">
-        <v>175</v>
+      <c r="A22" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B22" t="s" s="5">
+        <v>299</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>72</v>
@@ -2232,11 +2604,11 @@
       </c>
     </row>
     <row ht="25" r="23" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>74</v>
-      </c>
-      <c r="B23" t="s">
-        <v>176</v>
+      <c r="A23" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B23" t="s" s="5">
+        <v>300</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>73</v>
@@ -2265,7 +2637,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0F588A9-FD8A-4996-A530-60A12E52C8E8}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="6.0" collapsed="true"/>
@@ -2342,11 +2714,11 @@
       <c r="K3" s="7"/>
     </row>
     <row ht="13" r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" t="s">
-        <v>154</v>
+      <c r="A4" t="s" s="3">
+        <v>74</v>
+      </c>
+      <c r="B4" t="s" s="3">
+        <v>278</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>125</v>

--- a/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
+++ b/KatalonData/EmailTextToPay/BillFileLookUp_Demo.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="800" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="804" uniqueCount="303">
   <si>
     <t>Result</t>
   </si>
@@ -945,6 +945,12 @@
   </si>
   <si>
     <t>Thu Jul 09 18:07:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:00:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 17 21:01:03 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1432,7 @@
         <v>74</v>
       </c>
       <c r="B2" t="s" s="3">
-        <v>252</v>
+        <v>301</v>
       </c>
       <c r="C2" s="6" t="s">
         <v>10</v>
@@ -1446,7 +1452,7 @@
         <v>74</v>
       </c>
       <c r="B3" t="s" s="3">
-        <v>253</v>
+        <v>302</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
